--- a/tables/no_question_무질문모델_집계표.xlsx
+++ b/tables/no_question_무질문모델_집계표.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>모델A_기존분석</t>
+          <t>모델A_수정후분석</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>이용 희망 등을 전제한 기본대상 안내</t>
+          <t>v3 관측조건·일반안내 판정; 미관측 필요성 보존</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>기본대상 부합 수 6.02</t>
+          <t>수정 후 기본대상 부합 수 2.98</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
